--- a/worked_examples/AIHE-CASE09_ai_vendor_procurement_and_contract_negotiation/workbook/xlsx/AIHE-CASE09_worked_example_and_template.xlsx
+++ b/worked_examples/AIHE-CASE09_ai_vendor_procurement_and_contract_negotiation/workbook/xlsx/AIHE-CASE09_worked_example_and_template.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="Re61d11aa8c704f8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Inputs" sheetId="2" r:id="R21b7c427feab4a1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="3" r:id="Re14a2827c40042b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="R5ab399aa6c2b4da8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R973ded80246d433e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Inputs" sheetId="2" r:id="Rd289a60caa904928"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="3" r:id="R18a67e22e4b1463c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="R86931d00cd8c4548"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -44,8 +44,14 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF303236"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -77,6 +83,16 @@
         <x:fgColor rgb="FFFFF3CD"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2230"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F0E7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="36">
     <x:border/>
@@ -369,7 +385,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="101">
+  <x:cellXfs count="118">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -378,7 +394,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -386,7 +402,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -403,22 +419,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -435,22 +451,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -495,22 +511,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -525,22 +541,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -611,6 +627,53 @@
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -663,9 +726,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -774,25 +837,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>AI Vendor Procurement and Contract Negotiation</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
+      <x:c r="F1" s="102"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5"/>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="A2" s="102"/>
+      <x:c r="B2" s="102"/>
+      <x:c r="C2" s="102"/>
+      <x:c r="D2" s="102"/>
+      <x:c r="E2" s="102"/>
+      <x:c r="F2" s="102"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="21" t="str">
+      <x:c r="A4" s="104" t="str">
         <x:v>Example ID</x:v>
       </x:c>
       <x:c r="B4" s="42" t="str">
@@ -800,7 +863,7 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="22" t="str">
+      <x:c r="A5" s="106" t="str">
         <x:v>Chapter</x:v>
       </x:c>
       <x:c r="B5" s="43" t="str">
@@ -808,7 +871,7 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="22" t="str">
+      <x:c r="A6" s="106" t="str">
         <x:v>Decision question</x:v>
       </x:c>
       <x:c r="B6" s="43" t="str">
@@ -816,7 +879,7 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="22" t="str">
+      <x:c r="A7" s="106" t="str">
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B7" s="43" t="str">
@@ -824,7 +887,7 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="22" t="str">
+      <x:c r="A8" s="106" t="str">
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B8" s="43" t="str">
@@ -832,7 +895,7 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="22" t="str">
+      <x:c r="A9" s="106" t="str">
         <x:v>Release date</x:v>
       </x:c>
       <x:c r="B9" s="43" t="str">
@@ -840,7 +903,7 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="22" t="str">
+      <x:c r="A10" s="106" t="str">
         <x:v>How to use</x:v>
       </x:c>
       <x:c r="B10" s="43" t="str">
@@ -848,7 +911,7 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="22" t="str">
+      <x:c r="A11" s="106" t="str">
         <x:v>Related resources</x:v>
       </x:c>
       <x:c r="B11" s="43" t="str">
@@ -856,7 +919,7 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="23" t="str">
+      <x:c r="A12" s="108" t="str">
         <x:v>Data protection</x:v>
       </x:c>
       <x:c r="B12" s="44" t="str">
@@ -889,51 +952,51 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>Worked synthetic inputs and calculations</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-      <x:c r="H1" s="5"/>
-      <x:c r="I1" s="5"/>
-      <x:c r="J1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
+      <x:c r="F1" s="102"/>
+      <x:c r="G1" s="102"/>
+      <x:c r="H1" s="102"/>
+      <x:c r="I1" s="102"/>
+      <x:c r="J1" s="102"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="57" t="str">
+      <x:c r="A3" s="112" t="str">
         <x:v>Criterion</x:v>
       </x:c>
-      <x:c r="B3" s="58" t="str">
+      <x:c r="B3" s="113" t="str">
         <x:v>Weight</x:v>
       </x:c>
-      <x:c r="C3" s="58" t="str">
+      <x:c r="C3" s="113" t="str">
         <x:v>Vendor A score</x:v>
       </x:c>
-      <x:c r="D3" s="58" t="str">
+      <x:c r="D3" s="113" t="str">
         <x:v>Vendor B score</x:v>
       </x:c>
-      <x:c r="E3" s="59" t="str">
+      <x:c r="E3" s="114" t="str">
         <x:v>Mandatory</x:v>
       </x:c>
-      <x:c r="F3" s="57" t="str">
+      <x:c r="F3" s="112" t="str">
         <x:v>Vendor A weighted</x:v>
       </x:c>
-      <x:c r="G3" s="58" t="str">
+      <x:c r="G3" s="113" t="str">
         <x:v>Vendor B weighted</x:v>
       </x:c>
-      <x:c r="H3" s="58" t="str">
+      <x:c r="H3" s="113" t="str">
         <x:v>A safeguard failure</x:v>
       </x:c>
-      <x:c r="I3" s="59" t="str">
+      <x:c r="I3" s="114" t="str">
         <x:v>B safeguard failure</x:v>
       </x:c>
-      <x:c r="K3" s="57" t="str">
+      <x:c r="K3" s="112" t="str">
         <x:v>Summary</x:v>
       </x:c>
-      <x:c r="L3" s="59" t="str">
+      <x:c r="L3" s="114" t="str">
         <x:v>Formula result</x:v>
       </x:c>
     </x:row>
@@ -1269,28 +1332,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>Blank template - replace synthetic values with governed local evidence</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="57" t="str">
+      <x:c r="A3" s="112" t="str">
         <x:v>Criterion</x:v>
       </x:c>
-      <x:c r="B3" s="58" t="str">
+      <x:c r="B3" s="113" t="str">
         <x:v>Weight</x:v>
       </x:c>
-      <x:c r="C3" s="58" t="str">
+      <x:c r="C3" s="113" t="str">
         <x:v>Vendor A score</x:v>
       </x:c>
-      <x:c r="D3" s="58" t="str">
+      <x:c r="D3" s="113" t="str">
         <x:v>Vendor B score</x:v>
       </x:c>
-      <x:c r="E3" s="59" t="str">
+      <x:c r="E3" s="114" t="str">
         <x:v>Mandatory</x:v>
       </x:c>
     </x:row>
@@ -1414,28 +1477,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="102" t="str">
         <x:v>AI Vendor Procurement and Contract Negotiation</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="102"/>
+      <x:c r="C1" s="102"/>
+      <x:c r="D1" s="102"/>
+      <x:c r="E1" s="102"/>
+      <x:c r="F1" s="102"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5"/>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="A2" s="102"/>
+      <x:c r="B2" s="102"/>
+      <x:c r="C2" s="102"/>
+      <x:c r="D2" s="102"/>
+      <x:c r="E2" s="102"/>
+      <x:c r="F2" s="102"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="57" t="str">
+      <x:c r="A4" s="112" t="str">
         <x:v>Reference metric</x:v>
       </x:c>
-      <x:c r="B4" s="59" t="str">
+      <x:c r="B4" s="114" t="str">
         <x:v>Synthetic result</x:v>
       </x:c>
     </x:row>
@@ -1456,66 +1519,66 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="89" t="str">
+      <x:c r="A8" s="115" t="str">
         <x:v>Worked interpretation</x:v>
       </x:c>
-      <x:c r="B8" s="89"/>
-      <x:c r="C8" s="89"/>
-      <x:c r="D8" s="89"/>
-      <x:c r="E8" s="89"/>
-      <x:c r="F8" s="89"/>
+      <x:c r="B8" s="115"/>
+      <x:c r="C8" s="115"/>
+      <x:c r="D8" s="115"/>
+      <x:c r="E8" s="115"/>
+      <x:c r="F8" s="115"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="94" t="str">
+      <x:c r="A9" s="116" t="str">
         <x:v>Vendor A fails several mandatory safeguards, so its weighted average cannot justify selection. Vendor B may proceed to a controlled pilot after local evidence is verified, variable costs are capped, and monitoring and support are translated into enforceable service levels. Procurement value is the expected future value of the complete contract, not the lowest purchase price.</x:v>
       </x:c>
-      <x:c r="B9" s="94"/>
-      <x:c r="C9" s="94"/>
-      <x:c r="D9" s="94"/>
-      <x:c r="E9" s="94"/>
-      <x:c r="F9" s="94"/>
+      <x:c r="B9" s="116"/>
+      <x:c r="C9" s="116"/>
+      <x:c r="D9" s="116"/>
+      <x:c r="E9" s="116"/>
+      <x:c r="F9" s="116"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="94"/>
-      <x:c r="B10" s="94"/>
-      <x:c r="C10" s="94"/>
-      <x:c r="D10" s="94"/>
-      <x:c r="E10" s="94"/>
-      <x:c r="F10" s="94"/>
+      <x:c r="A10" s="116"/>
+      <x:c r="B10" s="116"/>
+      <x:c r="C10" s="116"/>
+      <x:c r="D10" s="116"/>
+      <x:c r="E10" s="116"/>
+      <x:c r="F10" s="116"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="94"/>
-      <x:c r="B11" s="94"/>
-      <x:c r="C11" s="94"/>
-      <x:c r="D11" s="94"/>
-      <x:c r="E11" s="94"/>
-      <x:c r="F11" s="94"/>
+      <x:c r="A11" s="116"/>
+      <x:c r="B11" s="116"/>
+      <x:c r="C11" s="116"/>
+      <x:c r="D11" s="116"/>
+      <x:c r="E11" s="116"/>
+      <x:c r="F11" s="116"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="94"/>
-      <x:c r="B12" s="94"/>
-      <x:c r="C12" s="94"/>
-      <x:c r="D12" s="94"/>
-      <x:c r="E12" s="94"/>
-      <x:c r="F12" s="94"/>
+      <x:c r="A12" s="116"/>
+      <x:c r="B12" s="116"/>
+      <x:c r="C12" s="116"/>
+      <x:c r="D12" s="116"/>
+      <x:c r="E12" s="116"/>
+      <x:c r="F12" s="116"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="94"/>
-      <x:c r="B13" s="94"/>
-      <x:c r="C13" s="94"/>
-      <x:c r="D13" s="94"/>
-      <x:c r="E13" s="94"/>
-      <x:c r="F13" s="94"/>
+      <x:c r="A13" s="116"/>
+      <x:c r="B13" s="116"/>
+      <x:c r="C13" s="116"/>
+      <x:c r="D13" s="116"/>
+      <x:c r="E13" s="116"/>
+      <x:c r="F13" s="116"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="100" t="str">
+      <x:c r="A15" s="117" t="str">
         <x:v>Interpret calculations with evidence quality, uncertainty, mandatory safeguards, implementation capacity, monitoring, and exit conditions.</x:v>
       </x:c>
-      <x:c r="B15" s="100"/>
-      <x:c r="C15" s="100"/>
-      <x:c r="D15" s="100"/>
-      <x:c r="E15" s="100"/>
-      <x:c r="F15" s="100"/>
+      <x:c r="B15" s="117"/>
+      <x:c r="C15" s="117"/>
+      <x:c r="D15" s="117"/>
+      <x:c r="E15" s="117"/>
+      <x:c r="F15" s="117"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
